--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 08/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 08/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.49601</v>
+        <v>16.75146</v>
       </c>
       <c r="D2" t="n">
-        <v>16.65066</v>
+        <v>16.18004</v>
       </c>
       <c r="E2" t="n">
-        <v>16.89927</v>
+        <v>16.50856</v>
       </c>
       <c r="F2" t="n">
-        <v>41.33021</v>
+        <v>41.24834</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0487</v>
+        <v>0.05036</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80728</v>
+        <v>1.8224</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.2562</v>
+        <v>16.81758</v>
       </c>
       <c r="D3" t="n">
-        <v>16.03722</v>
+        <v>16.02728</v>
       </c>
       <c r="E3" t="n">
-        <v>16.56901</v>
+        <v>16.39397</v>
       </c>
       <c r="F3" t="n">
-        <v>41.04518</v>
+        <v>42.1538</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05019</v>
+        <v>0.04991</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82889</v>
+        <v>1.81521</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.50128</v>
+        <v>16.65536</v>
       </c>
       <c r="D4" t="n">
-        <v>16.56547</v>
+        <v>16.23935</v>
       </c>
       <c r="E4" t="n">
-        <v>16.58568</v>
+        <v>16.57791</v>
       </c>
       <c r="F4" t="n">
-        <v>41.77108</v>
+        <v>41.52595</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04993</v>
+        <v>0.0505</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80451</v>
+        <v>1.80778</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.35633</v>
+        <v>16.8535</v>
       </c>
       <c r="D5" t="n">
-        <v>16.26672</v>
+        <v>16.2488</v>
       </c>
       <c r="E5" t="n">
-        <v>16.5962</v>
+        <v>16.41591</v>
       </c>
       <c r="F5" t="n">
-        <v>42.03754</v>
+        <v>42.54511</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04988</v>
+        <v>0.0504</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81959</v>
+        <v>1.74411</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.75658</v>
+        <v>16.62889</v>
       </c>
       <c r="D6" t="n">
-        <v>16.56519</v>
+        <v>16.14998</v>
       </c>
       <c r="E6" t="n">
-        <v>16.83858</v>
+        <v>16.59287</v>
       </c>
       <c r="F6" t="n">
-        <v>41.13178</v>
+        <v>42.02427</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0502</v>
+        <v>0.05062</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7973</v>
+        <v>1.79511</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.60692</v>
+        <v>16.65508</v>
       </c>
       <c r="D7" t="n">
-        <v>16.45034</v>
+        <v>16.28966</v>
       </c>
       <c r="E7" t="n">
-        <v>16.02073</v>
+        <v>16.59028</v>
       </c>
       <c r="F7" t="n">
-        <v>41.50069</v>
+        <v>42.53929</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05008</v>
+        <v>0.05051</v>
       </c>
       <c r="H7" t="n">
-        <v>1.78183</v>
+        <v>1.80491</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.52191</v>
+        <v>16.552</v>
       </c>
       <c r="D8" t="n">
-        <v>16.43018</v>
+        <v>16.4961</v>
       </c>
       <c r="E8" t="n">
-        <v>16.74255</v>
+        <v>16.52629</v>
       </c>
       <c r="F8" t="n">
-        <v>43.11902</v>
+        <v>42.3734</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04972</v>
+        <v>0.04993</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81299</v>
+        <v>1.79056</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.56585</v>
+        <v>16.52605</v>
       </c>
       <c r="D9" t="n">
-        <v>16.36994</v>
+        <v>16.24528</v>
       </c>
       <c r="E9" t="n">
-        <v>16.21058</v>
+        <v>16.49398</v>
       </c>
       <c r="F9" t="n">
-        <v>42.02522</v>
+        <v>41.64403</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04979</v>
+        <v>0.05037</v>
       </c>
       <c r="H9" t="n">
-        <v>1.76336</v>
+        <v>1.76235</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.36372</v>
+        <v>16.82579</v>
       </c>
       <c r="D10" t="n">
-        <v>16.41429</v>
+        <v>16.30683</v>
       </c>
       <c r="E10" t="n">
-        <v>16.69515</v>
+        <v>16.76207</v>
       </c>
       <c r="F10" t="n">
-        <v>41.36734</v>
+        <v>42.42267</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04952</v>
+        <v>0.05005</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81078</v>
+        <v>1.77116</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.58465</v>
+        <v>0.61075</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12128</v>
+        <v>1.10017</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60986</v>
+        <v>0.60371</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0953</v>
+        <v>1.10983</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.59832</v>
+        <v>0.58857</v>
       </c>
       <c r="D14" t="n">
-        <v>1.09603</v>
+        <v>1.0885</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.59423</v>
+        <v>0.59994</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1047</v>
+        <v>1.09671</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60822</v>
+        <v>0.58495</v>
       </c>
       <c r="D16" t="n">
-        <v>1.07687</v>
+        <v>1.10263</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6096</v>
+        <v>0.60062</v>
       </c>
       <c r="D17" t="n">
-        <v>1.09642</v>
+        <v>1.09957</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.60521</v>
+        <v>0.60207</v>
       </c>
       <c r="D18" t="n">
-        <v>1.08461</v>
+        <v>1.08799</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60529</v>
+        <v>0.58347</v>
       </c>
       <c r="D19" t="n">
-        <v>1.08679</v>
+        <v>1.09016</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.5848100000000001</v>
+        <v>0.59835</v>
       </c>
       <c r="D20" t="n">
-        <v>1.10227</v>
+        <v>1.1086</v>
       </c>
     </row>
   </sheetData>
